--- a/artfynd/A 62684-2025 artfynd.xlsx
+++ b/artfynd/A 62684-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ78"/>
+  <dimension ref="A1:AZ79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4985,54 +4985,49 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128786505</v>
+        <v>137414608</v>
       </c>
       <c r="B42" t="n">
-        <v>8455</v>
+        <v>58196</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hållbergsvägen, Dlr</t>
+          <t>Simmelok, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447762</v>
+        <v>447596</v>
       </c>
       <c r="R42" t="n">
-        <v>6784437</v>
+        <v>6784664</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5059,12 +5054,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5073,7 +5078,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5091,13 +5095,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128786505</t>
+          <t>https://artportalen.se/Sighting/137414608</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130746501</v>
+        <v>128786505</v>
       </c>
       <c r="B43" t="n">
         <v>8455</v>
@@ -5137,14 +5141,14 @@
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Evertsbergsvägen öst, Dlr</t>
+          <t>Hållbergsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447967</v>
+        <v>447762</v>
       </c>
       <c r="R43" t="n">
-        <v>6784475</v>
+        <v>6784437</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5171,12 +5175,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5203,13 +5207,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746501</t>
+          <t>https://artportalen.se/Sighting/128786505</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130746502</v>
+        <v>130746501</v>
       </c>
       <c r="B44" t="n">
         <v>8455</v>
@@ -5243,7 +5247,7 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -5253,10 +5257,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>447975</v>
+        <v>447967</v>
       </c>
       <c r="R44" t="n">
-        <v>6784493</v>
+        <v>6784475</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5315,13 +5319,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746502</t>
+          <t>https://artportalen.se/Sighting/130746501</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130746503</v>
+        <v>130746502</v>
       </c>
       <c r="B45" t="n">
         <v>8455</v>
@@ -5355,7 +5359,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5365,10 +5369,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>447933</v>
+        <v>447975</v>
       </c>
       <c r="R45" t="n">
-        <v>6784497</v>
+        <v>6784493</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5427,13 +5431,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746503</t>
+          <t>https://artportalen.se/Sighting/130746502</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130746504</v>
+        <v>130746503</v>
       </c>
       <c r="B46" t="n">
         <v>8455</v>
@@ -5477,10 +5481,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>447917</v>
+        <v>447933</v>
       </c>
       <c r="R46" t="n">
-        <v>6784459</v>
+        <v>6784497</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5539,13 +5543,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746504</t>
+          <t>https://artportalen.se/Sighting/130746503</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130746505</v>
+        <v>130746504</v>
       </c>
       <c r="B47" t="n">
         <v>8455</v>
@@ -5589,10 +5593,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>447906</v>
+        <v>447917</v>
       </c>
       <c r="R47" t="n">
-        <v>6784476</v>
+        <v>6784459</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5651,13 +5655,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746505</t>
+          <t>https://artportalen.se/Sighting/130746504</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130746506</v>
+        <v>130746505</v>
       </c>
       <c r="B48" t="n">
         <v>8455</v>
@@ -5701,10 +5705,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>447826</v>
+        <v>447906</v>
       </c>
       <c r="R48" t="n">
-        <v>6784573</v>
+        <v>6784476</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5763,13 +5767,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746506</t>
+          <t>https://artportalen.se/Sighting/130746505</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130746507</v>
+        <v>130746506</v>
       </c>
       <c r="B49" t="n">
         <v>8455</v>
@@ -5816,7 +5820,7 @@
         <v>447826</v>
       </c>
       <c r="R49" t="n">
-        <v>6784536</v>
+        <v>6784573</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5875,13 +5879,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746507</t>
+          <t>https://artportalen.se/Sighting/130746506</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130746508</v>
+        <v>130746507</v>
       </c>
       <c r="B50" t="n">
         <v>8455</v>
@@ -5925,10 +5929,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447816</v>
+        <v>447826</v>
       </c>
       <c r="R50" t="n">
-        <v>6784561</v>
+        <v>6784536</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5987,13 +5991,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746508</t>
+          <t>https://artportalen.se/Sighting/130746507</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130746510</v>
+        <v>130746508</v>
       </c>
       <c r="B51" t="n">
         <v>8455</v>
@@ -6037,10 +6041,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447718</v>
+        <v>447816</v>
       </c>
       <c r="R51" t="n">
-        <v>6784441</v>
+        <v>6784561</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6099,13 +6103,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746510</t>
+          <t>https://artportalen.se/Sighting/130746508</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130746511</v>
+        <v>130746510</v>
       </c>
       <c r="B52" t="n">
         <v>8455</v>
@@ -6149,10 +6153,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>447748</v>
+        <v>447718</v>
       </c>
       <c r="R52" t="n">
-        <v>6784472</v>
+        <v>6784441</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6211,13 +6215,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746511</t>
+          <t>https://artportalen.se/Sighting/130746510</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130746512</v>
+        <v>130746511</v>
       </c>
       <c r="B53" t="n">
         <v>8455</v>
@@ -6261,10 +6265,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447746</v>
+        <v>447748</v>
       </c>
       <c r="R53" t="n">
-        <v>6784500</v>
+        <v>6784472</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6323,13 +6327,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746512</t>
+          <t>https://artportalen.se/Sighting/130746511</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130746513</v>
+        <v>130746512</v>
       </c>
       <c r="B54" t="n">
         <v>8455</v>
@@ -6373,10 +6377,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>447735</v>
+        <v>447746</v>
       </c>
       <c r="R54" t="n">
-        <v>6784515</v>
+        <v>6784500</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6435,13 +6439,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746513</t>
+          <t>https://artportalen.se/Sighting/130746512</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130746515</v>
+        <v>130746513</v>
       </c>
       <c r="B55" t="n">
         <v>8455</v>
@@ -6475,7 +6479,7 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -6485,10 +6489,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447716</v>
+        <v>447735</v>
       </c>
       <c r="R55" t="n">
-        <v>6784496</v>
+        <v>6784515</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6547,13 +6551,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746515</t>
+          <t>https://artportalen.se/Sighting/130746513</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130746516</v>
+        <v>130746515</v>
       </c>
       <c r="B56" t="n">
         <v>8455</v>
@@ -6587,7 +6591,7 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -6597,10 +6601,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447725</v>
+        <v>447716</v>
       </c>
       <c r="R56" t="n">
-        <v>6784696</v>
+        <v>6784496</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6659,13 +6663,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746516</t>
+          <t>https://artportalen.se/Sighting/130746515</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130746517</v>
+        <v>130746516</v>
       </c>
       <c r="B57" t="n">
         <v>8455</v>
@@ -6709,10 +6713,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>447805</v>
+        <v>447725</v>
       </c>
       <c r="R57" t="n">
-        <v>6784562</v>
+        <v>6784696</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6771,13 +6775,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746517</t>
+          <t>https://artportalen.se/Sighting/130746516</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130746518</v>
+        <v>130746517</v>
       </c>
       <c r="B58" t="n">
         <v>8455</v>
@@ -6821,10 +6825,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>447815</v>
+        <v>447805</v>
       </c>
       <c r="R58" t="n">
-        <v>6784612</v>
+        <v>6784562</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6883,13 +6887,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746518</t>
+          <t>https://artportalen.se/Sighting/130746517</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130746519</v>
+        <v>130746518</v>
       </c>
       <c r="B59" t="n">
         <v>8455</v>
@@ -6923,7 +6927,7 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -6933,10 +6937,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>447826</v>
+        <v>447815</v>
       </c>
       <c r="R59" t="n">
-        <v>6784623</v>
+        <v>6784612</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6995,13 +6999,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746519</t>
+          <t>https://artportalen.se/Sighting/130746518</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130746520</v>
+        <v>130746519</v>
       </c>
       <c r="B60" t="n">
         <v>8455</v>
@@ -7035,7 +7039,7 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -7045,10 +7049,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>447846</v>
+        <v>447826</v>
       </c>
       <c r="R60" t="n">
-        <v>6784643</v>
+        <v>6784623</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7107,13 +7111,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746520</t>
+          <t>https://artportalen.se/Sighting/130746519</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130746521</v>
+        <v>130746520</v>
       </c>
       <c r="B61" t="n">
         <v>8455</v>
@@ -7157,10 +7161,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>447834</v>
+        <v>447846</v>
       </c>
       <c r="R61" t="n">
-        <v>6784604</v>
+        <v>6784643</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7219,13 +7223,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746521</t>
+          <t>https://artportalen.se/Sighting/130746520</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130746522</v>
+        <v>130746521</v>
       </c>
       <c r="B62" t="n">
         <v>8455</v>
@@ -7259,7 +7263,7 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -7269,10 +7273,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>447866</v>
+        <v>447834</v>
       </c>
       <c r="R62" t="n">
-        <v>6784597</v>
+        <v>6784604</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7331,13 +7335,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746522</t>
+          <t>https://artportalen.se/Sighting/130746521</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130746523</v>
+        <v>130746522</v>
       </c>
       <c r="B63" t="n">
         <v>8455</v>
@@ -7371,7 +7375,7 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -7381,10 +7385,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>447940</v>
+        <v>447866</v>
       </c>
       <c r="R63" t="n">
-        <v>6784589</v>
+        <v>6784597</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7443,13 +7447,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746523</t>
+          <t>https://artportalen.se/Sighting/130746522</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130746524</v>
+        <v>130746523</v>
       </c>
       <c r="B64" t="n">
         <v>8455</v>
@@ -7493,10 +7497,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>447932</v>
+        <v>447940</v>
       </c>
       <c r="R64" t="n">
-        <v>6784551</v>
+        <v>6784589</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7555,13 +7559,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746524</t>
+          <t>https://artportalen.se/Sighting/130746523</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130746525</v>
+        <v>130746524</v>
       </c>
       <c r="B65" t="n">
         <v>8455</v>
@@ -7605,10 +7609,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>447933</v>
+        <v>447932</v>
       </c>
       <c r="R65" t="n">
-        <v>6784552</v>
+        <v>6784551</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7667,13 +7671,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746525</t>
+          <t>https://artportalen.se/Sighting/130746524</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130746526</v>
+        <v>130746525</v>
       </c>
       <c r="B66" t="n">
         <v>8455</v>
@@ -7707,7 +7711,7 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -7717,10 +7721,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>447950</v>
+        <v>447933</v>
       </c>
       <c r="R66" t="n">
-        <v>6784549</v>
+        <v>6784552</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7779,13 +7783,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746526</t>
+          <t>https://artportalen.se/Sighting/130746525</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130746528</v>
+        <v>130746526</v>
       </c>
       <c r="B67" t="n">
         <v>8455</v>
@@ -7829,10 +7833,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>447952</v>
+        <v>447950</v>
       </c>
       <c r="R67" t="n">
-        <v>6784545</v>
+        <v>6784549</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7891,13 +7895,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746528</t>
+          <t>https://artportalen.se/Sighting/130746526</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130746530</v>
+        <v>130746528</v>
       </c>
       <c r="B68" t="n">
         <v>8455</v>
@@ -7931,7 +7935,7 @@
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -7941,10 +7945,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>447855</v>
+        <v>447952</v>
       </c>
       <c r="R68" t="n">
-        <v>6784599</v>
+        <v>6784545</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8003,13 +8007,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746530</t>
+          <t>https://artportalen.se/Sighting/130746528</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130746531</v>
+        <v>130746530</v>
       </c>
       <c r="B69" t="n">
         <v>8455</v>
@@ -8053,10 +8057,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>447932</v>
+        <v>447855</v>
       </c>
       <c r="R69" t="n">
-        <v>6784555</v>
+        <v>6784599</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8115,13 +8119,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130746531</t>
+          <t>https://artportalen.se/Sighting/130746530</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131073028</v>
+        <v>130746531</v>
       </c>
       <c r="B70" t="n">
         <v>8455</v>
@@ -8150,21 +8154,25 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Evertsbergsvägen öst, Evertsbergsvägen öst, Dlr</t>
+          <t>Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>447573</v>
+        <v>447932</v>
       </c>
       <c r="R70" t="n">
-        <v>6784308</v>
+        <v>6784555</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8191,22 +8199,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>12:17</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>12:17</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8215,6 +8213,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8232,16 +8231,16 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131073028</t>
+          <t>https://artportalen.se/Sighting/130746531</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132152152</v>
+        <v>131073028</v>
       </c>
       <c r="B71" t="n">
-        <v>8460</v>
+        <v>8455</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8269,19 +8268,19 @@
       <c r="I71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Hållbergsvägen, Hållbergsvägen, Dlr</t>
+          <t>Evertsbergsvägen öst, Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>447524</v>
+        <v>447573</v>
       </c>
       <c r="R71" t="n">
-        <v>6784261</v>
+        <v>6784308</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8308,22 +8307,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8349,13 +8348,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132152152</t>
+          <t>https://artportalen.se/Sighting/131073028</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132152776</v>
+        <v>132152152</v>
       </c>
       <c r="B72" t="n">
         <v>8460</v>
@@ -8391,14 +8390,14 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Evertsbergsvägen öst, Evertsbergsvägen öst, Dlr</t>
+          <t>Hållbergsvägen, Hållbergsvägen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>447492</v>
+        <v>447524</v>
       </c>
       <c r="R72" t="n">
-        <v>6784359</v>
+        <v>6784261</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8430,7 +8429,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8440,7 +8439,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8466,13 +8465,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132152776</t>
+          <t>https://artportalen.se/Sighting/132152152</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132152920</v>
+        <v>132152776</v>
       </c>
       <c r="B73" t="n">
         <v>8460</v>
@@ -8512,10 +8511,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>447481</v>
+        <v>447492</v>
       </c>
       <c r="R73" t="n">
-        <v>6784397</v>
+        <v>6784359</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8547,7 +8546,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8557,7 +8556,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8583,13 +8582,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132152920</t>
+          <t>https://artportalen.se/Sighting/132152776</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132153492</v>
+        <v>132152920</v>
       </c>
       <c r="B74" t="n">
         <v>8460</v>
@@ -8629,10 +8628,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>447376</v>
+        <v>447481</v>
       </c>
       <c r="R74" t="n">
-        <v>6784477</v>
+        <v>6784397</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8664,7 +8663,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8674,7 +8673,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8700,13 +8699,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132153492</t>
+          <t>https://artportalen.se/Sighting/132152920</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132153581</v>
+        <v>132153492</v>
       </c>
       <c r="B75" t="n">
         <v>8460</v>
@@ -8746,10 +8745,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>447395</v>
+        <v>447376</v>
       </c>
       <c r="R75" t="n">
-        <v>6784505</v>
+        <v>6784477</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8781,7 +8780,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8791,7 +8790,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8817,13 +8816,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132153581</t>
+          <t>https://artportalen.se/Sighting/132153492</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132154197</v>
+        <v>132153581</v>
       </c>
       <c r="B76" t="n">
         <v>8460</v>
@@ -8863,13 +8862,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>447308</v>
+        <v>447395</v>
       </c>
       <c r="R76" t="n">
-        <v>6784594</v>
+        <v>6784505</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8898,7 +8897,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8908,7 +8907,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8934,16 +8933,16 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132154197</t>
+          <t>https://artportalen.se/Sighting/132153581</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132154031</v>
+        <v>132154197</v>
       </c>
       <c r="B77" t="n">
-        <v>98060</v>
+        <v>8460</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8951,34 +8950,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Evertsbergsvägen öst, Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>447347</v>
+        <v>447308</v>
       </c>
       <c r="R77" t="n">
-        <v>6784550</v>
+        <v>6784594</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -9010,7 +9014,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9020,7 +9024,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9046,54 +9050,54 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132154031</t>
+          <t>https://artportalen.se/Sighting/132154197</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132152092</v>
+        <v>132154031</v>
       </c>
       <c r="B78" t="n">
-        <v>79374</v>
+        <v>98060</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>230405</v>
+        <v>221945</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Hållbergsvägen, Hållbergsvägen, Dlr</t>
+          <t>Evertsbergsvägen öst, Evertsbergsvägen öst, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>447535</v>
+        <v>447347</v>
       </c>
       <c r="R78" t="n">
-        <v>6784263</v>
+        <v>6784550</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9122,7 +9126,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9132,7 +9136,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9157,6 +9161,118 @@
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132154031</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>132152092</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79374</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Hållbergsvägen, Hållbergsvägen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>447535</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6784263</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132152092</t>
         </is>
@@ -9241,6 +9357,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62684-2025 artfynd.xlsx
+++ b/artfynd/A 62684-2025 artfynd.xlsx
@@ -4988,7 +4988,7 @@
         <v>137414608</v>
       </c>
       <c r="B42" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
